--- a/project/excel/cve.xlsx
+++ b/project/excel/cve.xlsx
@@ -801,84 +801,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>platforms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>collection_url</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>package_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>cpes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>modules</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>program_files</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>program_routines</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>repo</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>default_status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>versions</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>package_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>vendor</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>platforms</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"affected,unaffected,unknown"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2402,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2426,64 +2421,11 @@
           <t>containers</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cve_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>published_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>last_modified_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>products</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>weaknesses</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>references</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
+    </row>
+  </sheetData>
+  <dataValidations count="1">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CVE_RECORD"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ACTIVE,REJECTED,DISPUTED,RESERVED,DEPRECATED"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
